--- a/diabetes_prevalence_by_age_2021_tidy.xlsx
+++ b/diabetes_prevalence_by_age_2021_tidy.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5052e625e7f51e50/Desktop/health-data-dashboard/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MSI\OneDrive\Desktop\health-data-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{36E772E5-3791-4396-9899-67646C702181}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A936A96-33F3-47AD-9900-ED84FA8BF455}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1884" yWindow="1884" windowWidth="17280" windowHeight="8880" xr2:uid="{FC1FDFF0-8EFC-4A21-ACA7-F2082E07126E}"/>
+    <workbookView xWindow="2340" yWindow="2676" windowWidth="17280" windowHeight="8880" xr2:uid="{FC1FDFF0-8EFC-4A21-ACA7-F2082E07126E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>Age group</t>
   </si>
@@ -97,13 +97,22 @@
   </si>
   <si>
     <t>85+</t>
+  </si>
+  <si>
+    <t>Males_rate</t>
+  </si>
+  <si>
+    <t>Females_rate</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,###,###,##0.0"/>
+  </numFmts>
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -111,13 +120,25 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -132,8 +153,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -448,7 +472,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3A1C4F6-FFD2-491A-B816-B85172E64886}">
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.21875" customWidth="1"/>
@@ -456,7 +480,7 @@
     <col min="3" max="3" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -466,8 +490,14 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -477,8 +507,14 @@
       <c r="C2">
         <v>282</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D2" s="1">
+        <v>0</v>
+      </c>
+      <c r="E2" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -488,8 +524,14 @@
       <c r="C3">
         <v>1110</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D3" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="E3" s="1">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -499,8 +541,14 @@
       <c r="C4">
         <v>2521</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D4" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="E4" s="1">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -510,8 +558,14 @@
       <c r="C5">
         <v>3637</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D5" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="E5" s="1">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -521,8 +575,14 @@
       <c r="C6">
         <v>4835</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D6" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="E6" s="1">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -532,8 +592,14 @@
       <c r="C7">
         <v>6870</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D7" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="E7" s="1">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -543,8 +609,14 @@
       <c r="C8">
         <v>10442</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D8" s="1">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E8" s="1">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -554,8 +626,14 @@
       <c r="C9">
         <v>15371</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D9" s="1">
+        <v>1.8</v>
+      </c>
+      <c r="E9" s="1">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -565,8 +643,14 @@
       <c r="C10">
         <v>21012</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D10" s="1">
+        <v>3.1</v>
+      </c>
+      <c r="E10" s="1">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -576,8 +660,14 @@
       <c r="C11">
         <v>30777</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D11" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="E11" s="1">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>13</v>
       </c>
@@ -587,8 +677,14 @@
       <c r="C12">
         <v>45494</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D12" s="1">
+        <v>6.6</v>
+      </c>
+      <c r="E12" s="1">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>14</v>
       </c>
@@ -598,8 +694,14 @@
       <c r="C13">
         <v>58549</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D13" s="1">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="E13" s="1">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -609,8 +711,14 @@
       <c r="C14">
         <v>70266</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D14" s="1">
+        <v>12.3</v>
+      </c>
+      <c r="E14" s="1">
+        <v>9.3000000000000007</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>16</v>
       </c>
@@ -620,8 +728,14 @@
       <c r="C15">
         <v>76749</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D15" s="1">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="E15" s="1">
+        <v>11.6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -631,8 +745,14 @@
       <c r="C16">
         <v>79829</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D16" s="1">
+        <v>19.100000000000001</v>
+      </c>
+      <c r="E16" s="1">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -642,8 +762,14 @@
       <c r="C17">
         <v>67344</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D17" s="1">
+        <v>22.2</v>
+      </c>
+      <c r="E17" s="1">
+        <v>16.100000000000001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>19</v>
       </c>
@@ -653,8 +779,14 @@
       <c r="C18">
         <v>50777</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D18" s="1">
+        <v>22.1</v>
+      </c>
+      <c r="E18" s="1">
+        <v>17.2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -663,6 +795,12 @@
       </c>
       <c r="C19">
         <v>53345</v>
+      </c>
+      <c r="D19" s="1">
+        <v>21.3</v>
+      </c>
+      <c r="E19" s="1">
+        <v>16.399999999999999</v>
       </c>
     </row>
   </sheetData>
